--- a/daily_matches/job_matches_2026-04-28.xlsx
+++ b/daily_matches/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gappify</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d37540247c479f</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>SW/Agentic Engineer, Early Career</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Docker, Kubernetes, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+          <t>https://www.indeed.com/viewjob?jk=54066ace05109456</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Applications Program Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pansophic Learning</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Jenkins, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186a44966b498912</t>
+          <t>https://www.indeed.com/viewjob?jk=c3da39e418826fb3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Associate AI Engineer / AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pansophic Learning</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f5a74b17141f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=41a535507585dd6f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Associate AI Engineer / AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pansophic Learning</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61fbc863b2f656</t>
+          <t>https://www.indeed.com/viewjob?jk=fb0293a3422506f5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Monetization &amp; Decision Systems</t>
+          <t>Senior Product Associate-Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, XGBoost, LightGBM, Python, R, Scala</t>
+          <t>Generative AI, RAG, S3, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,287 +706,147 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d051a2cb03b6990b</t>
+          <t>https://www.indeed.com/viewjob?jk=53da743c89a3c74e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, Glue, Redshift, Data Lake, Redshift, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c91fb1173ff23885</t>
+          <t>https://www.indeed.com/viewjob?jk=7ddd609e45b7c084</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Burlington, VT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, Glue, Redshift, Data Lake, Redshift, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfbfb113d4a2bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb6bbaef0ba5ef7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, Glue, Redshift, Data Lake, Redshift, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a469c545b3f102</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea0d12996c496b4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Engineer (AI Driven Software Engineering, Java, Spring Boot, AWS) Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FIT:MATCH.AI</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c736a647fce4c9ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f93af729588ee4ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f14e14d98832164</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Aroha Technologies</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, MLflow, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f7113fe3fafcf1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Analyst- Construction Technology</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>VIVA Railings LLC</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0980ade5cd298a13</t>
+          <t>https://www.indeed.com/viewjob?jk=cea557739367886c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-28.xlsx
+++ b/daily_matches/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Kafka</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SW/Agentic Engineer, Early Career</t>
+          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Docker, Kubernetes, Terraform, Git, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54066ace05109456</t>
+          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, AWS SageMaker, MLflow, CI/CD, Jenkins, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=fbab8d66316f87e2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applications Program Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Silverchair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Jenkins, Git, Python, R</t>
+          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3da39e418826fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate AI Engineer / AI Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a535507585dd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=11e4622f245b9a1b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate AI Engineer / AI Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denham Springs, LA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, MLflow, Docker, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb0293a3422506f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e841927da214d3b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Product Associate-Data Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53da743c89a3c74e</t>
+          <t>https://www.indeed.com/viewjob?jk=2357e987f06fdaf3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Redshift, Data Lake, Redshift, R, Scala, Optimization</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ddd609e45b7c084</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Intern – Marketing Data Science &amp; Experimentation (MoneyLion, FinTech</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Redshift, Data Lake, Redshift, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,602 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb6bbaef0ba5ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=856704f9f1ee7603</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Redshift, Data Lake, Redshift, R, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea0d12996c496b4</t>
+          <t>https://www.indeed.com/viewjob?jk=38aebf4d79c53d9c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer (AI Driven Software Engineering, Java, Spring Boot, AWS) Remote</t>
+          <t>Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Impiricus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d05cb5b52382c31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer – LLM Applications (Azure)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59d448c07295c20d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Back-End Engineer (Healthcare Consulting)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sellers Dorsey</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14520627e91e655f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f68ce3be3e34bd80</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aureon</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ebab6abfc617c1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6304921fa0db780a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI and vision learning engineer (In person required)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SEC Industrial</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Peachtree Corners, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Docker, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Inizio Engage</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Myrtle Point, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8086ccd17758581</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist - Hybrid</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>National Interstate</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Richfield, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e476808ee5f683c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Multiple Software Engineering Roles – W2 Internal Direct Client</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BridgeNexus Technologies Inc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, MongoDB, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cea557739367886c</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4cb6d57a1158150</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Search and Recommendations</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa682aeb0c67c60a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Recommender System Engineer, AI-Driven (PICO-Lab) - San Jose</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24e9f71bdecbbacf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3419c8deb3a87c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Associate - AI Analyst</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, Git, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6350b5a19679660c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Field Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gradle Technologies</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20b4cce8f6133457</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-28.xlsx
+++ b/daily_matches/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfd90d1833c2dcd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
+          <t>Data Reliability Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, LangChain, RAG, S3, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
+          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, AWS SageMaker, MLflow, CI/CD, Jenkins, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Hadoop, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbab8d66316f87e2</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Search and Alerts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Silverchair</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka, Power BI, Python</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, EC2, Kinesis, CI/CD, Git, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e27c3a57395d5ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Junior AI Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Healthcare Revenue Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, S3, EC2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e4622f245b9a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b5611e31c7cfa6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denham Springs, LA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, MLflow, Docker, CI/CD, Git, PostgreSQL</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e841927da214d3b</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, BigQuery, Redshift, Python</t>
+          <t>RAG, S3, Glue, Redshift, Kubernetes, Git, Snowflake, Redshift, Hadoop, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2357e987f06fdaf3</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Redshift, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Intern – Marketing Data Science &amp; Experimentation (MoneyLion, FinTech</t>
+          <t>Sr. Platform Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856704f9f1ee7603</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6b4c7ac4b43263</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Platform Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38aebf4d79c53d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=570f64a7462c30d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer (Full-stack)</t>
+          <t>Sr. Platform Engineer I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Impiricus</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d05cb5b52382c31</t>
+          <t>https://www.indeed.com/viewjob?jk=e98da4e20aeecc7a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer – LLM Applications (Azure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d448c07295c20d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee730446d13184f5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Back-End Engineer (Healthcare Consulting)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sellers Dorsey</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14520627e91e655f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e0de9905682c3c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Programmer Analyst II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Texas State University</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>San Marcos, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, MySQL, MongoDB, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68ce3be3e34bd80</t>
+          <t>https://www.indeed.com/viewjob?jk=9882d0882e7d7531</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Cassandra, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=a22e56435129c080</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer - Integrations Team</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>AVO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebab6abfc617c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=918aad578920ca3e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering Intern - (Summer 2026)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tektronix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Solon, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6304921fa0db780a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2451a168bf60b5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Docker, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, Git, Databricks, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=616baba780dd65a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Inizio Engage</t>
+          <t>Life.Church</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8086ccd17758581</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5598845204585c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist - Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>National Interstate</t>
+          <t>Synack</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richfield, OH, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e476808ee5f683c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7db34dae3a26467</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Multiple Software Engineering Roles – W2 Internal Direct Client</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Healthcare Revenue Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Mistral, Pinecone, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cb6d57a1158150</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1e7afd1e1ea7d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analyst, Search and Recommendations</t>
+          <t>Senior PHP Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Gravity Lending</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+          <t>Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa682aeb0c67c60a</t>
+          <t>https://www.indeed.com/viewjob?jk=2459cc87c223e138</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Recommender System Engineer, AI-Driven (PICO-Lab) - San Jose</t>
+          <t>Senior Data Scientist, NLP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e9f71bdecbbacf</t>
+          <t>https://www.indeed.com/viewjob?jk=d84bb4f64356905d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Native Engineer, Growth Marketing</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cookunity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Snowflake, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3419c8deb3a87c</t>
+          <t>https://www.indeed.com/viewjob?jk=591fcde7d2cf0699</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Associate - AI Analyst</t>
+          <t>Engineer, Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Pinwheel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Git, Databricks, Python, SQL, R, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6350b5a19679660c</t>
+          <t>https://www.indeed.com/viewjob?jk=51b41608ec800248</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>IT Intern - AI-Driven Automation &amp; IoT Machine Monitoring</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gradle Technologies</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,147 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b4cce8f6133457</t>
+          <t>https://www.indeed.com/viewjob?jk=8931d572fee90fae</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e57cefbe19d99ccc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4eed162aeaceb8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68f992e1f2b377e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Research Scientist I (Intern) United States</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1d7adbaf5ac3b07</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-28.xlsx
+++ b/daily_matches/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer-Remote Opportunity</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Answer Financial Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfd90d1833c2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a536d9beed9da3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer/Software Engineer</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Diality Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, S3, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, Databricks</t>
+          <t>RAG, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
+          <t>https://www.indeed.com/viewjob?jk=089debbb9a2ef97f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Hadoop, PostgreSQL, NoSQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, S3, Glue, Redshift, Git, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=077ae16e340cf810</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Search and Alerts</t>
+          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, EC2, Kinesis, CI/CD, Git, MongoDB</t>
+          <t>Data Scientist, Machine Learning Engineer, S3, EC2, Glue, Athena, Redshift, Kinesis, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e27c3a57395d5ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior AI Software Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Healthcare Revenue Solutions</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, S3, EC2</t>
+          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, PySpark, Power BI, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b5611e31c7cfa6</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Terraform, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Redshift, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=b840c37f8e0d5d35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kubernetes, Git, Snowflake, Redshift, Hadoop, SQL</t>
+          <t>RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=84a91bd027b544af</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Junior AI/ML Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Grant Leading Technology, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Redshift, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Docker, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=eff8099dc24b005a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer I</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6b4c7ac4b43263</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer I</t>
+          <t>Sr. Advanced AI Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=570f64a7462c30d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9392556ac4945838</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer I</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Kaycha Labs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, RAG, LLaMA, Gemini, ChromaDB, FastAPI, Docker, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98da4e20aeecc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfde306fa7048cc4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Hadoop, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee730446d13184f5</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer / Azure Fabric Engineer Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Interlink Cloud Advisors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Synapse, Data Lake, CI/CD, Databricks, PySpark, Power BI, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e0de9905682c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=36e702ba08104800</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Programmer Analyst II</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Texas State University</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Marcos, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, MySQL, MongoDB, SQL, R, Scala</t>
+          <t>RAG, Copilot, Kubernetes, Git, Snowflake, Kafka, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9882d0882e7d7531</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Hadoop, PostgreSQL, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a22e56435129c080</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer - Integrations Team</t>
+          <t>Senior Software Engineer - Site Reliability Engineering (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Copilot, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918aad578920ca3e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea62067ada93585</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineering Intern - (Summer 2026)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tektronix</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Solon, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2451a168bf60b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Lake Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, CI/CD, Git, Databricks, Kafka, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Terraform, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616baba780dd65a8</t>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer, Development Tax Technology | Denver Summer/Fall 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Life.Church</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, AKS, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5598845204585c</t>
+          <t>https://www.indeed.com/viewjob?jk=00e39740ba057cea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI /ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Synack</t>
+          <t>GLOBO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, Pinecone, Prompt Engineering, Snowflake, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7db34dae3a26467</t>
+          <t>https://www.indeed.com/viewjob?jk=b38b339fd9acdc34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>AI Research Intern – Ribbon Research Labs (Co-op)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Healthcare Revenue Solutions</t>
+          <t>Ribbon Communications</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Pinecone, CI/CD, Python, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1e7afd1e1ea7d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b141bd041233a9f8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior PHP Developer</t>
+          <t>Java &amp; Angular Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gravity Lending</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2459cc87c223e138</t>
+          <t>https://www.indeed.com/viewjob?jk=57bb3ff67e9dd1c4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, NLP</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, S3, EC2, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84bb4f64356905d</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Native Engineer, Growth Marketing</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cookunity</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Snowflake, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591fcde7d2cf0699</t>
+          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer, Platform</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pinwheel</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b41608ec800248</t>
+          <t>https://www.indeed.com/viewjob?jk=ebca28711ea38fab</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Intern - AI-Driven Automation &amp; IoT Machine Monitoring</t>
+          <t>Senior AI-ML Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ceres</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8931d572fee90fae</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3a1b8aed56550b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Parallels</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, R, Optimization, Hypothesis Testing, A/B Testing</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57cefbe19d99ccc</t>
+          <t>https://www.indeed.com/viewjob?jk=db77999adbcfe196</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer II</t>
+          <t>AI Support Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>DataRobot</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,29 +1431,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eed162aeaceb8c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87394dac6e16ec</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f992e1f2b377e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f30db55d619a0b7d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Research Scientist I (Intern) United States</t>
+          <t>Senior Software Engineer — Data Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, Git, Python, R, Optimization</t>
+          <t>RAG, S3, EC2, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,77 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d7adbaf5ac3b07</t>
+          <t>https://www.indeed.com/viewjob?jk=73299ac147513066</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9eea570ae670787</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2a1122fdd2975e0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-28.xlsx
+++ b/daily_matches/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer-Remote Opportunity</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Answer Financial Inc.</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a536d9beed9da3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
+          <t>Associate Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diality Inc</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Docker, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089debbb9a2ef97f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bde994d264ae6b5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, S3, Glue, Redshift, Git, Redshift, Tableau</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077ae16e340cf810</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, S3, EC2, Glue, Athena, Redshift, Kinesis, Snowflake, Redshift</t>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, MLflow, CI/CD, Databricks, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8d476d6efaad50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Machine Learning Scientist III - Recommendations</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, PySpark, Power BI, Matplotlib, Seaborn, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Hadoop, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cf0c6d5d74dc29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Redshift, Git, Snowflake, Databricks, Redshift</t>
+          <t>AI Engineer, Data Scientist, RAG, S3, Redshift, CI/CD, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b840c37f8e0d5d35</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b08a232f4af96</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PySpark, Kafka</t>
+          <t>Data Scientist, Synapse, AKS, Git, Databricks, PySpark, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a91bd027b544af</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior AI/ML Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grant Leading Technology, LLC</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Docker, CI/CD, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff8099dc24b005a</t>
+          <t>https://www.indeed.com/viewjob?jk=294d6a4e5cf8f20f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>FluidStack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Power BI</t>
+          <t>Docker, CI/CD, Terraform, Git, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0e7673cf9fd64d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Advanced AI Software Engineer</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9392556ac4945838</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6c8fdde80076e9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>AI Full Stack Engineer Sr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kaycha Labs</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Gemini, ChromaDB, FastAPI, Docker, GitHub Actions, Git, Snowflake</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfde306fa7048cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d4cb4fc5fd72f9b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Hadoop, PostgreSQL, MySQL</t>
+          <t>RAG, Kubernetes, Terraform, Kafka, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=99c25210e5ea5f89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer / Azure Fabric Engineer Consultant</t>
+          <t>Senior Software Engineer in Test (AI Agentic Systems)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Interlink Cloud Advisors</t>
+          <t>Collective Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Synapse, Data Lake, CI/CD, Databricks, PySpark, Power BI, SQL</t>
+          <t>RAG, Gemini, Prompt Engineering, BigQuery, CI/CD, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e702ba08104800</t>
+          <t>https://www.indeed.com/viewjob?jk=a26135ad810377d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Inland Imaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Snowflake, Kafka, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,637 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NLM Cloud Engineer I</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Lexical Intelligence, LLC</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Hadoop, PostgreSQL, MySQL, MongoDB, SQL</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Site Reliability Engineering (Remote)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Copilot, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea62067ada93585</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Mid-Level Data Engineer, Global</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Vantage Data Centers</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Lake Data Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>E Source</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Terraform, Databricks, Kafka, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Engineer, Development Tax Technology | Denver Summer/Fall 2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, AKS, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00e39740ba057cea</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI /ML Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>GLOBO</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, Pinecone, Prompt Engineering, Snowflake, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b38b339fd9acdc34</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Research Intern – Ribbon Research Labs (Co-op)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Ribbon Communications</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Westford, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b141bd041233a9f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Java &amp; Angular Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, MongoDB, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57bb3ff67e9dd1c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dealpath</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, S3, EC2, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Databricks Architect</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stitch Consulting Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebca28711ea38fab</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior AI-ML Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3a1b8aed56550b</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Parallels</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, R, Optimization, Hypothesis Testing, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db77999adbcfe196</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AI Support Engineer II</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DataRobot</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87394dac6e16ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f30db55d619a0b7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer — Data Platform</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Databricks, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73299ac147513066</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Forward Deployment Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Flock Safety</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9eea570ae670787</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Forward Deployment Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Flock</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a1122fdd2975e0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc592b752043b64c</t>
         </is>
       </c>
     </row>
